--- a/exc3/Техрадар.xlsx
+++ b/exc3/Техрадар.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\spint11\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\sprint11\exc3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D7307C-2ADA-4676-95FE-552023CE8166}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D649085B-EFF6-4EF6-BC0A-210C0FC421A4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C8E3E517-DD30-45C5-B0C4-4713EBD35391}"/>
+    <workbookView xWindow="2175" yWindow="1725" windowWidth="17025" windowHeight="8475" xr2:uid="{C8E3E517-DD30-45C5-B0C4-4713EBD35391}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -63,9 +63,6 @@
     <t>Apache Kafka</t>
   </si>
   <si>
-    <t>Новая шина данных, уже внедряется для доменов (финтех, ИИ), скоро для клиник.</t>
-  </si>
-  <si>
     <t>Apache Airflow</t>
   </si>
   <si>
@@ -115,6 +112,9 @@
   </si>
   <si>
     <t>Asset</t>
+  </si>
+  <si>
+    <t>Потоковая плафторма, уже внедряется для доменов (финтех, ИИ), скоро для клиник.</t>
   </si>
 </sst>
 </file>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="4:6" ht="30" x14ac:dyDescent="0.25">
@@ -542,10 +542,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="4:6" ht="30" x14ac:dyDescent="0.25">
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="7" spans="4:6" ht="30" x14ac:dyDescent="0.25">
@@ -564,54 +564,54 @@
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8" spans="4:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" spans="4:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="10" spans="4:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="11" spans="4:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="12" spans="4:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -625,7 +625,7 @@
     <row r="20" spans="7:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
